--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C33C936A-2739-49E5-A3CA-3B6A2C8785A4}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{241D6D18-DE21-405B-8472-BB20FCFEDC32}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1775,7 +1775,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B22" s="14">
         <v>400</v>
@@ -1820,158 +1820,326 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B23" s="14">
+        <v>430</v>
+      </c>
+      <c r="C23" s="14">
+        <v>40</v>
+      </c>
+      <c r="D23" s="14">
+        <v>140</v>
+      </c>
+      <c r="E23" s="14">
+        <v>90</v>
+      </c>
+      <c r="F23" s="14">
+        <v>350</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7</v>
+      </c>
+      <c r="H23" s="14">
+        <v>340</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B24" s="14">
+        <v>460</v>
+      </c>
+      <c r="C24" s="14">
+        <v>20</v>
+      </c>
+      <c r="D24" s="14">
+        <v>250</v>
+      </c>
+      <c r="E24" s="14">
+        <v>210</v>
+      </c>
+      <c r="F24" s="14">
+        <v>100</v>
+      </c>
+      <c r="G24" s="14">
+        <v>2</v>
+      </c>
+      <c r="H24" s="14">
+        <v>253</v>
+      </c>
+      <c r="I24" s="15">
+        <f t="shared" ref="I24:I28" si="2">IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
+        <v>1293</v>
+      </c>
+      <c r="J24" s="15">
+        <f t="shared" ref="J24:J28" si="3">IF(I24="","",1440-I24)</f>
+        <v>147</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>46240</v>
+      </c>
+      <c r="B25" s="14">
+        <v>460</v>
+      </c>
+      <c r="C25" s="14">
+        <v>20</v>
+      </c>
+      <c r="D25" s="14">
+        <v>230</v>
+      </c>
+      <c r="E25" s="14">
+        <v>180</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>310</v>
+      </c>
+      <c r="I25" s="15">
+        <f t="shared" si="2"/>
+        <v>1200</v>
+      </c>
+      <c r="J25" s="15">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
+        <v>46241</v>
+      </c>
+      <c r="B26" s="14">
+        <v>460</v>
+      </c>
+      <c r="C26" s="14">
+        <v>20</v>
+      </c>
+      <c r="D26" s="14">
+        <v>230</v>
+      </c>
+      <c r="E26" s="14">
+        <v>180</v>
+      </c>
+      <c r="F26" s="14">
+        <v>90</v>
+      </c>
+      <c r="G26" s="14">
+        <v>3</v>
+      </c>
+      <c r="H26" s="14">
+        <v>310</v>
+      </c>
+      <c r="I26" s="15">
+        <f t="shared" si="2"/>
+        <v>1290</v>
+      </c>
+      <c r="J26" s="15">
+        <f t="shared" si="3"/>
+        <v>150</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B27" s="14">
+        <v>400</v>
+      </c>
+      <c r="C27" s="14">
+        <v>30</v>
+      </c>
+      <c r="D27" s="14">
+        <v>150</v>
+      </c>
+      <c r="E27" s="14">
+        <v>120</v>
+      </c>
+      <c r="F27" s="14">
+        <v>350</v>
+      </c>
+      <c r="G27" s="14">
+        <v>7</v>
+      </c>
+      <c r="H27" s="14">
+        <v>200</v>
+      </c>
+      <c r="I27" s="15">
+        <f t="shared" si="2"/>
+        <v>1250</v>
+      </c>
+      <c r="J27" s="15">
+        <f t="shared" si="3"/>
+        <v>190</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>240</v>
+      </c>
+      <c r="E28" s="14">
+        <v>130</v>
+      </c>
+      <c r="F28" s="14">
+        <v>200</v>
+      </c>
+      <c r="G28" s="14">
+        <v>4</v>
+      </c>
+      <c r="H28" s="14">
+        <v>250</v>
+      </c>
+      <c r="I28" s="15">
+        <f t="shared" si="2"/>
+        <v>1260</v>
+      </c>
+      <c r="J28" s="15">
+        <f t="shared" si="3"/>
+        <v>180</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B29" s="14">
+        <v>430</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>180</v>
+      </c>
+      <c r="E29" s="14">
+        <v>120</v>
+      </c>
+      <c r="F29" s="14">
+        <v>350</v>
+      </c>
+      <c r="G29" s="14">
+        <v>7</v>
+      </c>
+      <c r="H29" s="14">
+        <v>220</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
@@ -2863,11 +3031,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2885,11 +3053,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2907,11 +3075,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2929,11 +3097,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2951,11 +3119,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2973,11 +3141,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2995,11 +3163,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3017,11 +3185,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3039,11 +3207,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3061,11 +3229,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3083,11 +3251,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3105,11 +3273,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3127,11 +3295,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3149,11 +3317,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3171,11 +3339,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3193,11 +3361,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3215,11 +3383,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3237,11 +3405,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3259,11 +3427,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3281,11 +3449,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3303,11 +3471,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3325,11 +3493,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3347,11 +3515,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3369,11 +3537,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3391,11 +3559,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3413,11 +3581,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3435,11 +3603,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3457,11 +3625,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3479,11 +3647,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3501,11 +3669,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3523,11 +3691,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3545,11 +3713,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3567,11 +3735,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3589,11 +3757,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3611,11 +3779,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3633,11 +3801,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3655,11 +3823,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3677,11 +3845,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3699,11 +3867,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3721,11 +3889,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3743,11 +3911,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3765,11 +3933,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3787,11 +3955,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3809,11 +3977,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3831,11 +3999,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3853,11 +4021,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3875,11 +4043,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3897,11 +4065,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3919,11 +4087,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3941,11 +4109,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3963,11 +4131,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3985,11 +4153,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4007,11 +4175,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4029,11 +4197,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4051,11 +4219,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4073,11 +4241,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4095,11 +4263,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4117,11 +4285,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4139,11 +4307,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4161,11 +4329,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4183,11 +4351,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4205,11 +4373,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4227,11 +4395,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4249,11 +4417,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4271,11 +4439,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4293,11 +4461,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4315,11 +4483,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4337,11 +4505,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4359,11 +4527,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4381,11 +4549,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4403,11 +4571,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4425,11 +4593,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4447,11 +4615,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4469,11 +4637,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4491,11 +4659,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4513,11 +4681,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4535,11 +4703,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4557,11 +4725,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4579,11 +4747,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4601,11 +4769,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4623,11 +4791,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4645,11 +4813,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4667,11 +4835,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4689,11 +4857,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4711,11 +4879,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4733,11 +4901,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4755,11 +4923,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4777,11 +4945,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4799,11 +4967,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4821,11 +4989,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4843,11 +5011,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4865,11 +5033,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4887,11 +5055,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4909,11 +5077,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4931,11 +5099,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4953,11 +5121,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4975,11 +5143,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4997,11 +5165,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5019,11 +5187,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5041,11 +5209,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5063,11 +5231,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5085,11 +5253,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5107,11 +5275,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5129,11 +5297,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5151,11 +5319,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5173,11 +5341,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5195,11 +5363,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5217,11 +5385,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5239,11 +5407,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5261,11 +5429,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5283,11 +5451,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5305,11 +5473,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5327,11 +5495,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5349,11 +5517,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5371,11 +5539,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5393,11 +5561,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5415,11 +5583,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5437,11 +5605,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5459,11 +5627,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5481,11 +5649,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5503,11 +5671,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5525,11 +5693,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5547,11 +5715,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5569,11 +5737,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5591,11 +5759,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5613,11 +5781,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5635,11 +5803,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5657,11 +5825,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5679,11 +5847,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5701,11 +5869,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5723,11 +5891,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5745,11 +5913,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5767,11 +5935,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5789,11 +5957,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5811,11 +5979,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5833,11 +6001,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5855,11 +6023,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5877,11 +6045,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5899,11 +6067,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5921,11 +6089,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5943,11 +6111,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5965,11 +6133,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5987,11 +6155,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6009,11 +6177,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6031,11 +6199,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6053,11 +6221,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6075,11 +6243,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6097,11 +6265,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6119,11 +6287,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6141,11 +6309,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6163,11 +6331,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6185,11 +6353,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6207,11 +6375,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6229,11 +6397,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6251,11 +6419,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6273,11 +6441,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6295,11 +6463,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6317,11 +6485,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6339,11 +6507,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6361,11 +6529,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6383,11 +6551,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6405,11 +6573,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6427,11 +6595,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6449,11 +6617,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6471,11 +6639,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6493,11 +6661,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6515,11 +6683,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6537,11 +6705,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6559,11 +6727,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6581,11 +6749,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6603,11 +6771,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6625,11 +6793,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6647,11 +6815,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6669,11 +6837,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6691,11 +6859,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6713,11 +6881,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6735,11 +6903,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6757,11 +6925,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6779,11 +6947,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6801,11 +6969,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6823,11 +6991,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6845,11 +7013,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6867,11 +7035,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6889,11 +7057,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6911,11 +7079,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6933,11 +7101,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6955,11 +7123,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6977,11 +7145,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6999,11 +7167,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7021,11 +7189,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7043,11 +7211,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7065,11 +7233,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7087,11 +7255,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7109,11 +7277,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7131,11 +7299,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7153,11 +7321,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7175,11 +7343,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7197,11 +7365,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7219,11 +7387,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7241,11 +7409,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7263,11 +7431,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7285,11 +7453,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7307,11 +7475,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7329,11 +7497,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7351,11 +7519,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7373,11 +7541,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7395,11 +7563,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7417,11 +7585,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7439,11 +7607,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7461,11 +7629,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7483,11 +7651,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7505,11 +7673,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7527,11 +7695,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7549,11 +7717,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7571,11 +7739,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7593,11 +7761,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7615,11 +7783,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7637,11 +7805,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7659,11 +7827,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7681,11 +7849,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7703,11 +7871,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7725,11 +7893,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7747,11 +7915,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7769,11 +7937,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7791,11 +7959,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7813,11 +7981,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7835,11 +8003,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7857,11 +8025,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7879,11 +8047,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7901,11 +8069,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7923,11 +8091,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7945,11 +8113,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7967,11 +8135,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7989,11 +8157,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8011,11 +8179,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8033,11 +8201,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8055,11 +8223,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8077,11 +8245,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8099,11 +8267,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8121,11 +8289,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8143,11 +8311,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8165,11 +8333,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8187,11 +8355,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8209,11 +8377,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8231,11 +8399,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8253,11 +8421,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8275,11 +8443,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8297,11 +8465,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8319,11 +8487,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8341,11 +8509,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8363,11 +8531,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8385,11 +8553,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8407,11 +8575,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8429,11 +8597,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8451,11 +8619,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8473,11 +8641,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8495,11 +8663,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8517,11 +8685,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8539,11 +8707,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8561,11 +8729,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8583,11 +8751,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8605,11 +8773,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8627,11 +8795,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8649,11 +8817,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8671,11 +8839,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8693,11 +8861,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8715,11 +8883,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8737,11 +8905,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8759,11 +8927,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8781,11 +8949,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8803,11 +8971,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8825,11 +8993,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8847,11 +9015,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8869,11 +9037,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8891,11 +9059,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8913,11 +9081,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8935,11 +9103,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8957,11 +9125,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8979,11 +9147,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9001,11 +9169,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9023,11 +9191,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9045,11 +9213,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9067,11 +9235,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9089,11 +9257,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9111,11 +9279,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9133,11 +9301,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9155,11 +9323,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9177,11 +9345,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9199,11 +9367,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9221,11 +9389,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9243,11 +9411,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9265,11 +9433,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9287,11 +9455,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9309,11 +9477,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9331,11 +9499,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9353,11 +9521,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9375,11 +9543,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9397,11 +9565,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9419,11 +9587,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9441,11 +9609,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9463,11 +9631,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9485,11 +9653,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9507,11 +9675,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9529,11 +9697,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9551,11 +9719,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9573,11 +9741,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9595,11 +9763,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9617,11 +9785,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9639,11 +9807,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9661,11 +9829,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9683,11 +9851,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9705,11 +9873,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9727,11 +9895,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9749,11 +9917,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9771,11 +9939,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9793,11 +9961,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9815,11 +9983,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9837,11 +10005,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9859,11 +10027,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9881,11 +10049,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9903,11 +10071,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9925,11 +10093,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9947,11 +10115,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9969,11 +10137,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9991,11 +10159,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10013,11 +10181,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10035,11 +10203,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10057,11 +10225,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10079,11 +10247,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10101,11 +10269,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10123,11 +10291,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10145,11 +10313,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{241D6D18-DE21-405B-8472-BB20FCFEDC32}"/>
+  <xr:revisionPtr revIDLastSave="186" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17132E16-A059-4E1A-83BA-4738524A1118}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>good</t>
+  </si>
+  <si>
+    <t>to day learn git&amp;github</t>
   </si>
 </sst>
 </file>
@@ -2142,26 +2145,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B30" s="14">
+        <v>450</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>300</v>
+      </c>
+      <c r="E30" s="14">
+        <v>250</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>300</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="186" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17132E16-A059-4E1A-83BA-4738524A1118}"/>
+  <xr:revisionPtr revIDLastSave="205" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93F01A82-8AE6-4592-AEDE-446012F655C5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>to day learn git&amp;github</t>
+  </si>
+  <si>
+    <t>practice git&amp;github</t>
   </si>
 </sst>
 </file>
@@ -2152,30 +2155,30 @@
         <v>450</v>
       </c>
       <c r="C30" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D30" s="14">
-        <v>300</v>
+        <v>170</v>
       </c>
       <c r="E30" s="14">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="F30" s="14">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="G30" s="14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H30" s="14">
         <v>300</v>
       </c>
       <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v>1300</v>
+        <v>1420</v>
       </c>
       <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="K30" s="16" t="s">
         <v>64</v>
@@ -2191,26 +2194,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B31" s="14">
+        <v>440</v>
+      </c>
+      <c r="C31" s="14">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
+        <v>400</v>
+      </c>
+      <c r="E31" s="14">
+        <v>120</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>300</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="205" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93F01A82-8AE6-4592-AEDE-446012F655C5}"/>
+  <xr:revisionPtr revIDLastSave="218" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16EC1FFF-18C8-45CF-A370-0F85296D9F72}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,6 +260,12 @@
   </si>
   <si>
     <t>practice git&amp;github</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>I am confused about course</t>
   </si>
 </sst>
 </file>
@@ -2240,26 +2246,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B32" s="14">
+        <v>40</v>
+      </c>
+      <c r="C32" s="14">
+        <v>30</v>
+      </c>
+      <c r="D32" s="14">
+        <v>410</v>
+      </c>
+      <c r="E32" s="14">
+        <v>130</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>350</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>

--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="218" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16EC1FFF-18C8-45CF-A370-0F85296D9F72}"/>
+  <xr:revisionPtr revIDLastSave="249" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21A49414-882E-4B82-BF42-11626C59E87A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2250,7 +2250,7 @@
         <v>46278</v>
       </c>
       <c r="B32" s="14">
-        <v>40</v>
+        <v>420</v>
       </c>
       <c r="C32" s="14">
         <v>30</v>
@@ -2272,11 +2272,11 @@
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1340</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>100</v>
       </c>
       <c r="K32" s="16" t="s">
         <v>56</v>
@@ -2292,48 +2292,96 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B33" s="14">
+        <v>420</v>
+      </c>
+      <c r="C33" s="14">
+        <v>30</v>
+      </c>
+      <c r="D33" s="14">
+        <v>350</v>
+      </c>
+      <c r="E33" s="14">
+        <v>140</v>
+      </c>
+      <c r="F33" s="14">
+        <v>100</v>
+      </c>
+      <c r="G33" s="14">
+        <v>2</v>
+      </c>
+      <c r="H33" s="14">
+        <v>340</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B34" s="14">
+        <v>410</v>
+      </c>
+      <c r="C34" s="14">
+        <v>20</v>
+      </c>
+      <c r="D34" s="14">
+        <v>120</v>
+      </c>
+      <c r="E34" s="14">
+        <v>120</v>
+      </c>
+      <c r="F34" s="14">
+        <v>350</v>
+      </c>
+      <c r="G34" s="14">
+        <v>7</v>
+      </c>
+      <c r="H34" s="14">
+        <v>320</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>

--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="249" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21A49414-882E-4B82-BF42-11626C59E87A}"/>
+  <xr:revisionPtr revIDLastSave="253" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67B50595-3D41-494A-BE29-648A8FBA9CA0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2384,26 +2384,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+      <c r="A35" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B35" s="14">
+        <v>430</v>
+      </c>
+      <c r="C35" s="14">
+        <v>40</v>
+      </c>
+      <c r="D35" s="14">
+        <v>140</v>
+      </c>
+      <c r="E35" s="14">
+        <v>90</v>
+      </c>
+      <c r="F35" s="14">
+        <v>200</v>
+      </c>
+      <c r="G35" s="14">
+        <v>4</v>
+      </c>
+      <c r="H35" s="14">
+        <v>340</v>
+      </c>
+      <c r="I35" s="15">
+        <f t="shared" ref="I35" si="4">IF(SUM(B35:F35,H35)=0,"",SUM(B35:F35,H35))</f>
+        <v>1240</v>
+      </c>
+      <c r="J35" s="15">
+        <f t="shared" ref="J35" si="5">IF(I35="","",1440-I35)</f>
+        <v>200</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>
@@ -3163,11 +3187,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3185,11 +3209,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3207,11 +3231,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3229,11 +3253,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3251,11 +3275,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3273,11 +3297,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3295,11 +3319,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3317,11 +3341,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3339,11 +3363,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3361,11 +3385,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3383,11 +3407,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3405,11 +3429,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3427,11 +3451,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3449,11 +3473,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3471,11 +3495,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3493,11 +3517,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3515,11 +3539,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3537,11 +3561,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3559,11 +3583,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3581,11 +3605,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3603,11 +3627,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3625,11 +3649,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3647,11 +3671,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3669,11 +3693,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3691,11 +3715,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3713,11 +3737,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3735,11 +3759,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3757,11 +3781,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3779,11 +3803,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3801,11 +3825,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3823,11 +3847,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3845,11 +3869,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3867,11 +3891,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3889,11 +3913,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3911,11 +3935,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3933,11 +3957,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3955,11 +3979,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3977,11 +4001,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3999,11 +4023,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4021,11 +4045,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4043,11 +4067,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4065,11 +4089,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4087,11 +4111,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4109,11 +4133,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4131,11 +4155,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4153,11 +4177,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4175,11 +4199,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4197,11 +4221,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4219,11 +4243,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4241,11 +4265,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4263,11 +4287,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4285,11 +4309,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4307,11 +4331,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4329,11 +4353,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4351,11 +4375,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4373,11 +4397,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4395,11 +4419,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4417,11 +4441,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4439,11 +4463,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4461,11 +4485,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4483,11 +4507,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4505,11 +4529,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4527,11 +4551,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4549,11 +4573,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4571,11 +4595,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="8">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="9">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4593,11 +4617,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4615,11 +4639,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4637,11 +4661,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4659,11 +4683,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4681,11 +4705,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4703,11 +4727,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4725,11 +4749,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4747,11 +4771,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4769,11 +4793,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4791,11 +4815,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4813,11 +4837,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4835,11 +4859,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4857,11 +4881,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4879,11 +4903,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4901,11 +4925,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4923,11 +4947,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4945,11 +4969,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4967,11 +4991,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4989,11 +5013,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5011,11 +5035,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5033,11 +5057,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5055,11 +5079,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5077,11 +5101,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5099,11 +5123,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5121,11 +5145,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5143,11 +5167,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5165,11 +5189,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5187,11 +5211,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5209,11 +5233,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5231,11 +5255,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5253,11 +5277,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5275,11 +5299,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5297,11 +5321,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5319,11 +5343,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5341,11 +5365,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5363,11 +5387,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5385,11 +5409,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5407,11 +5431,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5429,11 +5453,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5451,11 +5475,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5473,11 +5497,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5495,11 +5519,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5517,11 +5541,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5539,11 +5563,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5561,11 +5585,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5583,11 +5607,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5605,11 +5629,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5627,11 +5651,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5649,11 +5673,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5671,11 +5695,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5693,11 +5717,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5715,11 +5739,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5737,11 +5761,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5759,11 +5783,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5781,11 +5805,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5803,11 +5827,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5825,11 +5849,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5847,11 +5871,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5869,11 +5893,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5891,11 +5915,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5913,11 +5937,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5935,11 +5959,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5957,11 +5981,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5979,11 +6003,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="10">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="11">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6001,11 +6025,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6023,11 +6047,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6045,11 +6069,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6067,11 +6091,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6089,11 +6113,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6111,11 +6135,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6133,11 +6157,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6155,11 +6179,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6177,11 +6201,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6199,11 +6223,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6221,11 +6245,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6243,11 +6267,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6265,11 +6289,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6287,11 +6311,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6309,11 +6333,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6331,11 +6355,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6353,11 +6377,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6375,11 +6399,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6397,11 +6421,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6419,11 +6443,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6441,11 +6465,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6463,11 +6487,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6485,11 +6509,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6507,11 +6531,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6529,11 +6553,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6551,11 +6575,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6573,11 +6597,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6595,11 +6619,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6617,11 +6641,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6639,11 +6663,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6661,11 +6685,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6683,11 +6707,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6705,11 +6729,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6727,11 +6751,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6749,11 +6773,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6771,11 +6795,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6793,11 +6817,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6815,11 +6839,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6837,11 +6861,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6859,11 +6883,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6881,11 +6905,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6903,11 +6927,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6925,11 +6949,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6947,11 +6971,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6969,11 +6993,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6991,11 +7015,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7013,11 +7037,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7035,11 +7059,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7057,11 +7081,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7079,11 +7103,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7101,11 +7125,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7123,11 +7147,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7145,11 +7169,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7167,11 +7191,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7189,11 +7213,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7211,11 +7235,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7233,11 +7257,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7255,11 +7279,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7277,11 +7301,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7299,11 +7323,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7321,11 +7345,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7343,11 +7367,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7365,11 +7389,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7387,11 +7411,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="12">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="13">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7409,11 +7433,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7431,11 +7455,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7453,11 +7477,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7475,11 +7499,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7497,11 +7521,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7519,11 +7543,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7541,11 +7565,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7563,11 +7587,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7585,11 +7609,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7607,11 +7631,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7629,11 +7653,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7651,11 +7675,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7673,11 +7697,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7695,11 +7719,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7717,11 +7741,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7739,11 +7763,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7761,11 +7785,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7783,11 +7807,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7805,11 +7829,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7827,11 +7851,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7849,11 +7873,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7871,11 +7895,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7893,11 +7917,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7915,11 +7939,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7937,11 +7961,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7959,11 +7983,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7981,11 +8005,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -8003,11 +8027,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8025,11 +8049,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8047,11 +8071,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8069,11 +8093,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8091,11 +8115,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8113,11 +8137,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8135,11 +8159,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8157,11 +8181,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8179,11 +8203,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8201,11 +8225,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8223,11 +8247,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8245,11 +8269,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8267,11 +8291,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8289,11 +8313,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8311,11 +8335,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8333,11 +8357,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8355,11 +8379,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8377,11 +8401,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8399,11 +8423,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8421,11 +8445,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8443,11 +8467,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8465,11 +8489,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8487,11 +8511,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8509,11 +8533,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8531,11 +8555,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8553,11 +8577,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8575,11 +8599,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8597,11 +8621,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8619,11 +8643,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8641,11 +8665,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8663,11 +8687,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8685,11 +8709,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8707,11 +8731,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8729,11 +8753,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8751,11 +8775,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8773,11 +8797,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8795,11 +8819,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="14">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="15">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8817,11 +8841,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8839,11 +8863,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8861,11 +8885,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8883,11 +8907,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8905,11 +8929,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8927,11 +8951,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8949,11 +8973,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8971,11 +8995,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8993,11 +9017,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -9015,11 +9039,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -9037,11 +9061,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9059,11 +9083,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9081,11 +9105,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9103,11 +9127,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9125,11 +9149,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9147,11 +9171,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9169,11 +9193,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9191,11 +9215,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9213,11 +9237,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9235,11 +9259,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9257,11 +9281,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9279,11 +9303,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9301,11 +9325,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9323,11 +9347,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9345,11 +9369,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9367,11 +9391,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9389,11 +9413,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9411,11 +9435,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9433,11 +9457,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9455,11 +9479,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9477,11 +9501,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9499,11 +9523,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9521,11 +9545,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9543,11 +9567,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9565,11 +9589,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9587,11 +9611,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9609,11 +9633,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9631,11 +9655,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9653,11 +9677,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9675,11 +9699,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9697,11 +9721,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9719,11 +9743,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9741,11 +9765,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9763,11 +9787,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9785,11 +9809,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9807,11 +9831,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9829,11 +9853,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9851,11 +9875,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9873,11 +9897,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9895,11 +9919,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9917,11 +9941,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9939,11 +9963,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9961,11 +9985,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9983,11 +10007,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -10005,11 +10029,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10027,11 +10051,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10049,11 +10073,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10071,11 +10095,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10093,11 +10117,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10115,11 +10139,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10137,11 +10161,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10159,11 +10183,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10181,11 +10205,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10203,11 +10227,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="16">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="17">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10225,11 +10249,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10247,11 +10271,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10269,11 +10293,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10291,11 +10315,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10313,11 +10337,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10335,11 +10359,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10357,11 +10381,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10379,11 +10403,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10401,11 +10425,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10423,11 +10447,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10445,11 +10469,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="253" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67B50595-3D41-494A-BE29-648A8FBA9CA0}"/>
+  <xr:revisionPtr revIDLastSave="268" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D95E44A2-6341-4191-9901-C73F956E7643}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>I am confused about course</t>
+  </si>
+  <si>
+    <t>to day learn python</t>
   </si>
 </sst>
 </file>
@@ -2430,26 +2433,50 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B36" s="14">
+        <v>390</v>
+      </c>
+      <c r="C36" s="14">
+        <v>20</v>
+      </c>
+      <c r="D36" s="14">
+        <v>220</v>
+      </c>
+      <c r="E36" s="14">
+        <v>130</v>
+      </c>
+      <c r="F36" s="14">
+        <v>350</v>
+      </c>
+      <c r="G36" s="14">
+        <v>7</v>
+      </c>
+      <c r="H36" s="14">
+        <v>215</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1325</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>115</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>

--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="268" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D95E44A2-6341-4191-9901-C73F956E7643}"/>
+  <xr:revisionPtr revIDLastSave="273" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7472C8D9-AA05-462F-A224-8B0D50F3534A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2479,26 +2479,50 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+      <c r="A37" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B37" s="14">
+        <v>420</v>
+      </c>
+      <c r="C37" s="14">
+        <v>20</v>
+      </c>
+      <c r="D37" s="14">
+        <v>220</v>
+      </c>
+      <c r="E37" s="14">
+        <v>122</v>
+      </c>
+      <c r="F37" s="14">
+        <v>350</v>
+      </c>
+      <c r="G37" s="14">
+        <v>7</v>
+      </c>
+      <c r="H37" s="14">
+        <v>180</v>
+      </c>
+      <c r="I37" s="15">
+        <f t="shared" ref="I37" si="6">IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
+        <v>1312</v>
+      </c>
+      <c r="J37" s="15">
+        <f t="shared" ref="J37" si="7">IF(I37="","",1440-I37)</f>
+        <v>128</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>
@@ -3214,11 +3238,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="8">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="9">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3236,11 +3260,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3258,11 +3282,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3280,11 +3304,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3302,11 +3326,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3324,11 +3348,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3346,11 +3370,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3368,11 +3392,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3390,11 +3414,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3412,11 +3436,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3434,11 +3458,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3456,11 +3480,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3478,11 +3502,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3500,11 +3524,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3522,11 +3546,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3544,11 +3568,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3566,11 +3590,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3588,11 +3612,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3610,11 +3634,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3632,11 +3656,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3654,11 +3678,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3676,11 +3700,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3698,11 +3722,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3720,11 +3744,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3742,11 +3766,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3764,11 +3788,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3786,11 +3810,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3808,11 +3832,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3830,11 +3854,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3852,11 +3876,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3874,11 +3898,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3896,11 +3920,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3918,11 +3942,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3940,11 +3964,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3962,11 +3986,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3984,11 +4008,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -4006,11 +4030,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -4028,11 +4052,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -4050,11 +4074,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4072,11 +4096,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4094,11 +4118,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4116,11 +4140,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4138,11 +4162,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4160,11 +4184,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4182,11 +4206,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4204,11 +4228,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4226,11 +4250,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4248,11 +4272,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4270,11 +4294,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4292,11 +4316,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4314,11 +4338,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4336,11 +4360,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4358,11 +4382,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4380,11 +4404,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4402,11 +4426,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4424,11 +4448,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4446,11 +4470,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4468,11 +4492,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4490,11 +4514,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4512,11 +4536,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4534,11 +4558,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4556,11 +4580,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4578,11 +4602,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4600,11 +4624,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4622,11 +4646,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="8">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="10">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="9">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="11">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4644,11 +4668,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4666,11 +4690,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4688,11 +4712,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4710,11 +4734,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4732,11 +4756,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4754,11 +4778,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4776,11 +4800,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4798,11 +4822,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4820,11 +4844,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4842,11 +4866,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4864,11 +4888,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4886,11 +4910,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4908,11 +4932,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4930,11 +4954,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4952,11 +4976,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4974,11 +4998,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4996,11 +5020,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -5018,11 +5042,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -5040,11 +5064,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5062,11 +5086,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5084,11 +5108,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5106,11 +5130,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5128,11 +5152,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5150,11 +5174,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5172,11 +5196,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5194,11 +5218,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5216,11 +5240,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5238,11 +5262,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5260,11 +5284,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5282,11 +5306,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5304,11 +5328,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5326,11 +5350,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5348,11 +5372,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5370,11 +5394,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5392,11 +5416,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5414,11 +5438,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5436,11 +5460,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5458,11 +5482,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5480,11 +5504,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5502,11 +5526,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5524,11 +5548,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5546,11 +5570,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5568,11 +5592,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5590,11 +5614,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5612,11 +5636,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5634,11 +5658,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5656,11 +5680,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5678,11 +5702,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5700,11 +5724,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5722,11 +5746,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5744,11 +5768,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5766,11 +5790,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5788,11 +5812,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5810,11 +5834,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5832,11 +5856,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5854,11 +5878,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5876,11 +5900,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5898,11 +5922,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5920,11 +5944,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5942,11 +5966,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5964,11 +5988,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5986,11 +6010,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6008,11 +6032,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6030,11 +6054,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="10">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="12">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="11">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="13">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6052,11 +6076,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6074,11 +6098,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6096,11 +6120,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6118,11 +6142,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6140,11 +6164,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6162,11 +6186,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6184,11 +6208,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6206,11 +6230,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6228,11 +6252,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6250,11 +6274,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6272,11 +6296,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6294,11 +6318,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6316,11 +6340,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6338,11 +6362,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6360,11 +6384,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6382,11 +6406,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6404,11 +6428,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6426,11 +6450,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6448,11 +6472,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6470,11 +6494,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6492,11 +6516,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6514,11 +6538,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6536,11 +6560,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6558,11 +6582,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6580,11 +6604,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6602,11 +6626,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6624,11 +6648,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6646,11 +6670,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6668,11 +6692,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6690,11 +6714,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6712,11 +6736,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6734,11 +6758,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6756,11 +6780,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6778,11 +6802,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6800,11 +6824,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6822,11 +6846,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6844,11 +6868,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6866,11 +6890,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6888,11 +6912,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6910,11 +6934,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6932,11 +6956,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6954,11 +6978,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6976,11 +7000,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6998,11 +7022,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -7020,11 +7044,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -7042,11 +7066,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7064,11 +7088,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7086,11 +7110,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7108,11 +7132,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7130,11 +7154,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7152,11 +7176,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7174,11 +7198,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7196,11 +7220,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7218,11 +7242,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7240,11 +7264,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7262,11 +7286,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7284,11 +7308,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7306,11 +7330,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7328,11 +7352,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7350,11 +7374,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7372,11 +7396,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7394,11 +7418,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7416,11 +7440,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7438,11 +7462,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="12">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="14">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="13">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="15">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7460,11 +7484,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7482,11 +7506,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7504,11 +7528,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7526,11 +7550,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7548,11 +7572,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7570,11 +7594,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7592,11 +7616,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7614,11 +7638,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7636,11 +7660,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7658,11 +7682,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7680,11 +7704,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7702,11 +7726,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7724,11 +7748,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7746,11 +7770,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7768,11 +7792,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7790,11 +7814,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7812,11 +7836,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7834,11 +7858,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7856,11 +7880,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7878,11 +7902,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7900,11 +7924,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7922,11 +7946,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7944,11 +7968,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7966,11 +7990,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7988,11 +8012,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -8010,11 +8034,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -8032,11 +8056,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -8054,11 +8078,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8076,11 +8100,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8098,11 +8122,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8120,11 +8144,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8142,11 +8166,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8164,11 +8188,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8186,11 +8210,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8208,11 +8232,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8230,11 +8254,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8252,11 +8276,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8274,11 +8298,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8296,11 +8320,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8318,11 +8342,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8340,11 +8364,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8362,11 +8386,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8384,11 +8408,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8406,11 +8430,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8428,11 +8452,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8450,11 +8474,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8472,11 +8496,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8494,11 +8518,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8516,11 +8540,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8538,11 +8562,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8560,11 +8584,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8582,11 +8606,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8604,11 +8628,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8626,11 +8650,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8648,11 +8672,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8670,11 +8694,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8692,11 +8716,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8714,11 +8738,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8736,11 +8760,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8758,11 +8782,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8780,11 +8804,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8802,11 +8826,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8824,11 +8848,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8846,11 +8870,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="14">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="16">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="15">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="17">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8868,11 +8892,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8890,11 +8914,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8912,11 +8936,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8934,11 +8958,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8956,11 +8980,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8978,11 +9002,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -9000,11 +9024,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -9022,11 +9046,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -9044,11 +9068,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -9066,11 +9090,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -9088,11 +9112,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9110,11 +9134,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9132,11 +9156,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9154,11 +9178,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9176,11 +9200,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9198,11 +9222,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9220,11 +9244,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9242,11 +9266,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9264,11 +9288,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9286,11 +9310,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9308,11 +9332,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9330,11 +9354,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9352,11 +9376,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9374,11 +9398,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9396,11 +9420,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9418,11 +9442,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9440,11 +9464,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9462,11 +9486,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9484,11 +9508,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9506,11 +9530,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9528,11 +9552,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9550,11 +9574,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9572,11 +9596,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9594,11 +9618,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9616,11 +9640,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9638,11 +9662,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9660,11 +9684,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9682,11 +9706,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9704,11 +9728,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9726,11 +9750,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9748,11 +9772,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9770,11 +9794,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9792,11 +9816,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9814,11 +9838,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9836,11 +9860,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9858,11 +9882,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9880,11 +9904,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9902,11 +9926,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9924,11 +9948,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9946,11 +9970,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9968,11 +9992,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9990,11 +10014,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -10012,11 +10036,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -10034,11 +10058,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -10056,11 +10080,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10078,11 +10102,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10100,11 +10124,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10122,11 +10146,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10144,11 +10168,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10166,11 +10190,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10188,11 +10212,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10210,11 +10234,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10232,11 +10256,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10254,11 +10278,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="16">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="18">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="17">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="19">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10276,11 +10300,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10298,11 +10322,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10320,11 +10344,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10342,11 +10366,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10364,11 +10388,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10386,11 +10410,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10408,11 +10432,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10430,11 +10454,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10452,11 +10476,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10474,11 +10498,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10496,11 +10520,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="273" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7472C8D9-AA05-462F-A224-8B0D50F3534A}"/>
+  <xr:revisionPtr revIDLastSave="278" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B4B2084-EAD2-4FE8-8532-DF57AB7AA8E0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2504,11 +2504,11 @@
         <v>180</v>
       </c>
       <c r="I37" s="15">
-        <f t="shared" ref="I37" si="6">IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
+        <f t="shared" ref="I37:I38" si="6">IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
         <v>1312</v>
       </c>
       <c r="J37" s="15">
-        <f t="shared" ref="J37" si="7">IF(I37="","",1440-I37)</f>
+        <f t="shared" ref="J37:J38" si="7">IF(I37="","",1440-I37)</f>
         <v>128</v>
       </c>
       <c r="K37" s="16" t="s">
@@ -2525,26 +2525,50 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+      <c r="A38" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B38" s="14">
+        <v>430</v>
+      </c>
+      <c r="C38" s="14">
+        <v>20</v>
+      </c>
+      <c r="D38" s="14">
+        <v>490</v>
+      </c>
+      <c r="E38" s="14">
+        <v>140</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>310</v>
+      </c>
+      <c r="I38" s="15">
+        <f t="shared" si="6"/>
+        <v>1390</v>
+      </c>
+      <c r="J38" s="15">
+        <f t="shared" si="7"/>
+        <v>50</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>

--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="278" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B4B2084-EAD2-4FE8-8532-DF57AB7AA8E0}"/>
+  <xr:revisionPtr revIDLastSave="282" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{216993D9-8A20-4F63-8EC9-6BC727EB2344}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2504,11 +2504,11 @@
         <v>180</v>
       </c>
       <c r="I37" s="15">
-        <f t="shared" ref="I37:I38" si="6">IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
+        <f t="shared" ref="I37:I39" si="6">IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
         <v>1312</v>
       </c>
       <c r="J37" s="15">
-        <f t="shared" ref="J37:J38" si="7">IF(I37="","",1440-I37)</f>
+        <f t="shared" ref="J37:J39" si="7">IF(I37="","",1440-I37)</f>
         <v>128</v>
       </c>
       <c r="K37" s="16" t="s">
@@ -2526,7 +2526,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13">
-        <v>46253</v>
+        <v>46284</v>
       </c>
       <c r="B38" s="14">
         <v>430</v>
@@ -2571,26 +2571,50 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+      <c r="A39" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B39" s="14">
+        <v>450</v>
+      </c>
+      <c r="C39" s="14">
+        <v>40</v>
+      </c>
+      <c r="D39" s="14">
+        <v>360</v>
+      </c>
+      <c r="E39" s="14">
+        <v>180</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>280</v>
+      </c>
+      <c r="I39" s="15">
+        <f t="shared" si="6"/>
+        <v>1310</v>
+      </c>
+      <c r="J39" s="15">
+        <f t="shared" si="7"/>
+        <v>130</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>

--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="282" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{216993D9-8A20-4F63-8EC9-6BC727EB2344}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAE3D553-76C2-4DAC-BE2D-1EA1979BBF87}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2617,26 +2617,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B40" s="14">
+        <v>410</v>
+      </c>
+      <c r="C40" s="14">
+        <v>20</v>
+      </c>
+      <c r="D40" s="14">
+        <v>320</v>
+      </c>
+      <c r="E40" s="14">
+        <v>100</v>
+      </c>
+      <c r="F40" s="14">
+        <v>50</v>
+      </c>
+      <c r="G40" s="14">
+        <v>2</v>
+      </c>
+      <c r="H40" s="14">
+        <v>450</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>90</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>

--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="295" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAE3D553-76C2-4DAC-BE2D-1EA1979BBF87}"/>
+  <xr:revisionPtr revIDLastSave="307" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61FAB106-D0E3-4DDC-9E4E-C6990EF19716}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3384" yWindow="2436" windowWidth="17280" windowHeight="9960" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>to day learn python</t>
+  </si>
+  <si>
+    <t>good productive day</t>
   </si>
 </sst>
 </file>
@@ -2663,26 +2666,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B41" s="14">
+        <v>420</v>
+      </c>
+      <c r="C41" s="14">
+        <v>20</v>
+      </c>
+      <c r="D41" s="14">
+        <v>210</v>
+      </c>
+      <c r="E41" s="14">
+        <v>100</v>
+      </c>
+      <c r="F41" s="14">
+        <v>350</v>
+      </c>
+      <c r="G41" s="14">
+        <v>7</v>
+      </c>
+      <c r="H41" s="14">
+        <v>200</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="307" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61FAB106-D0E3-4DDC-9E4E-C6990EF19716}"/>
+  <xr:revisionPtr revIDLastSave="320" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{075D37AC-4A3B-4E12-848D-81955AB4F0B9}"/>
   <bookViews>
     <workbookView xWindow="3384" yWindow="2436" windowWidth="17280" windowHeight="9960" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2712,26 +2712,50 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B42" s="14">
+        <v>430</v>
+      </c>
+      <c r="C42" s="14">
+        <v>20</v>
+      </c>
+      <c r="D42" s="14">
+        <v>180</v>
+      </c>
+      <c r="E42" s="14">
+        <v>150</v>
+      </c>
+      <c r="F42" s="14">
+        <v>250</v>
+      </c>
+      <c r="G42" s="14">
+        <v>4</v>
+      </c>
+      <c r="H42" s="14">
+        <v>300</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>

--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="320" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{075D37AC-4A3B-4E12-848D-81955AB4F0B9}"/>
+  <xr:revisionPtr revIDLastSave="334" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5D4B6C4-205C-4CC6-8F97-67C23C58286F}"/>
   <bookViews>
-    <workbookView xWindow="3384" yWindow="2436" windowWidth="17280" windowHeight="9960" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>good productive day</t>
+  </si>
+  <si>
+    <t>to day prepear for ca</t>
   </si>
 </sst>
 </file>
@@ -2758,26 +2761,50 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B43" s="14">
+        <v>400</v>
+      </c>
+      <c r="C43" s="14">
+        <v>15</v>
+      </c>
+      <c r="D43" s="14">
+        <v>190</v>
+      </c>
+      <c r="E43" s="14">
+        <v>100</v>
+      </c>
+      <c r="F43" s="14">
+        <v>350</v>
+      </c>
+      <c r="G43" s="14">
+        <v>7</v>
+      </c>
+      <c r="H43" s="14">
+        <v>250</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1305</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>135</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>
